--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -433,9 +433,23 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3">
+        <v>34</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -419,37 +419,9 @@
         <v>备注</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-09-17</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2">
-        <v>116.73</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-09-18</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3">
-        <v>34</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -419,9 +419,37 @@
         <v>备注</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2">
+        <v>116.73</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3">
+        <v>34</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -447,9 +447,23 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -421,13 +421,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-01</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2">
-        <v>116.73</v>
+        <v>52.07</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -435,13 +435,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-17</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>116.73</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -449,21 +449,35 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4">
+        <v>34</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>2026-09-24</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>100</v>
       </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -435,13 +435,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-02</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3">
-        <v>116.73</v>
+        <v>68.35</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -449,13 +449,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-17</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>116.73</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -463,21 +463,35 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5">
+        <v>34</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
         <v>2026-09-24</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>100</v>
       </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -449,13 +449,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-03</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4">
-        <v>116.73</v>
+        <v>8.9</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -463,13 +463,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-17</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>116.73</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -477,21 +477,35 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6">
+        <v>34</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>2026-09-24</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>100</v>
       </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -463,13 +463,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-04</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5">
-        <v>116.73</v>
+        <v>51.81</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -477,13 +477,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-17</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>116.73</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -491,21 +491,35 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7">
+        <v>34</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>2026-09-24</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>100</v>
       </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -477,13 +477,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6">
-        <v>116.73</v>
+        <v>109.97</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -491,13 +491,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-17</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>116.73</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -505,21 +505,35 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8">
+        <v>34</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>2026-09-24</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>100</v>
       </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -491,13 +491,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-06</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7">
-        <v>116.73</v>
+        <v>107.89</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -505,13 +505,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-17</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8">
-        <v>34</v>
+        <v>116.73</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -519,21 +519,35 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9">
+        <v>34</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v>2026-09-24</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>100</v>
       </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -505,13 +505,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-07</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8">
-        <v>116.73</v>
+        <v>66.65</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -519,13 +519,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-17</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9">
-        <v>34</v>
+        <v>116.73</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -533,21 +533,35 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10">
+        <v>34</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>2026-09-24</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>100</v>
       </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D25"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -423,8 +423,8 @@
       <c r="A2" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>100</v>
       </c>
       <c r="C2">
         <v>52.07</v>
@@ -437,8 +437,8 @@
       <c r="A3" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>100</v>
       </c>
       <c r="C3">
         <v>68.35</v>
@@ -451,8 +451,8 @@
       <c r="A4" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>100</v>
       </c>
       <c r="C4">
         <v>8.9</v>
@@ -465,8 +465,8 @@
       <c r="A5" t="str">
         <v>2026-09-04</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>100</v>
       </c>
       <c r="C5">
         <v>51.81</v>
@@ -479,8 +479,8 @@
       <c r="A6" t="str">
         <v>2026-09-05</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>100</v>
       </c>
       <c r="C6">
         <v>109.97</v>
@@ -493,8 +493,8 @@
       <c r="A7" t="str">
         <v>2026-09-06</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>100</v>
       </c>
       <c r="C7">
         <v>107.89</v>
@@ -507,8 +507,8 @@
       <c r="A8" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>100</v>
       </c>
       <c r="C8">
         <v>66.65</v>
@@ -519,13 +519,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-09-17</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
+        <v>2026-09-08</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
       </c>
       <c r="C9">
-        <v>116.73</v>
+        <v>261.88</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -533,13 +533,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-09-18</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10">
-        <v>34</v>
+        <v>2026-09-09</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -547,21 +547,217 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-09-12</v>
+      </c>
+      <c r="B13">
+        <v>100</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="B14">
+        <v>100</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="B15">
+        <v>100</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="B16">
+        <v>100</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="B17">
+        <v>100</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+      <c r="C18">
+        <v>116.73</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B19">
+        <v>100</v>
+      </c>
+      <c r="C19">
+        <v>34</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-09-19</v>
+      </c>
+      <c r="B20">
+        <v>100</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-09-20</v>
+      </c>
+      <c r="B21">
+        <v>100</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="B22">
+        <v>100</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="B23">
+        <v>100</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="B24">
+        <v>100</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
         <v>2026-09-24</v>
       </c>
-      <c r="B11">
-        <v>100</v>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
+      <c r="B25">
+        <v>100</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -538,8 +538,8 @@
       <c r="B10">
         <v>100</v>
       </c>
-      <c r="C10" t="str">
-        <v/>
+      <c r="C10">
+        <v>169.07</v>
       </c>
       <c r="D10" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -552,8 +552,8 @@
       <c r="B11">
         <v>100</v>
       </c>
-      <c r="C11" t="str">
-        <v/>
+      <c r="C11">
+        <v>133.83</v>
       </c>
       <c r="D11" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -580,8 +580,8 @@
       <c r="B13">
         <v>100</v>
       </c>
-      <c r="C13" t="str">
-        <v/>
+      <c r="C13">
+        <v>174.38</v>
       </c>
       <c r="D13" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -566,8 +566,8 @@
       <c r="B12">
         <v>100</v>
       </c>
-      <c r="C12" t="str">
-        <v/>
+      <c r="C12">
+        <v>363.51</v>
       </c>
       <c r="D12" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -594,8 +594,8 @@
       <c r="B14">
         <v>100</v>
       </c>
-      <c r="C14" t="str">
-        <v/>
+      <c r="C14">
+        <v>167.94</v>
       </c>
       <c r="D14" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -608,8 +608,8 @@
       <c r="B15">
         <v>100</v>
       </c>
-      <c r="C15" t="str">
-        <v/>
+      <c r="C15">
+        <v>38.03</v>
       </c>
       <c r="D15" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -622,8 +622,8 @@
       <c r="B16">
         <v>100</v>
       </c>
-      <c r="C16" t="str">
-        <v/>
+      <c r="C16">
+        <v>60.76</v>
       </c>
       <c r="D16" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -636,8 +636,8 @@
       <c r="B17">
         <v>100</v>
       </c>
-      <c r="C17" t="str">
-        <v/>
+      <c r="C17">
+        <v>32.09</v>
       </c>
       <c r="D17" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -651,7 +651,7 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>116.73</v>
+        <v>116.86</v>
       </c>
       <c r="D18" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -665,7 +665,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>34</v>
+        <v>105.2</v>
       </c>
       <c r="D19" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -678,8 +678,8 @@
       <c r="B20">
         <v>100</v>
       </c>
-      <c r="C20" t="str">
-        <v/>
+      <c r="C20">
+        <v>91.97</v>
       </c>
       <c r="D20" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -692,8 +692,8 @@
       <c r="B21">
         <v>100</v>
       </c>
-      <c r="C21" t="str">
-        <v/>
+      <c r="C21">
+        <v>4.99</v>
       </c>
       <c r="D21" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -706,8 +706,8 @@
       <c r="B22">
         <v>100</v>
       </c>
-      <c r="C22" t="str">
-        <v/>
+      <c r="C22">
+        <v>54.06</v>
       </c>
       <c r="D22" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -720,8 +720,8 @@
       <c r="B23">
         <v>100</v>
       </c>
-      <c r="C23" t="str">
-        <v/>
+      <c r="C23">
+        <v>37.81</v>
       </c>
       <c r="D23" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -734,8 +734,8 @@
       <c r="B24">
         <v>100</v>
       </c>
-      <c r="C24" t="str">
-        <v/>
+      <c r="C24">
+        <v>43.01</v>
       </c>
       <c r="D24" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -748,8 +748,8 @@
       <c r="B25">
         <v>100</v>
       </c>
-      <c r="C25" t="str">
-        <v/>
+      <c r="C25">
+        <v>14.6</v>
       </c>
       <c r="D25" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D30"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -749,15 +749,85 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>14.6</v>
+        <v>167.9</v>
       </c>
       <c r="D25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-09-25</v>
+      </c>
+      <c r="B26">
+        <v>100</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="B27">
+        <v>100</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -762,8 +762,8 @@
       <c r="B26">
         <v>100</v>
       </c>
-      <c r="C26" t="str">
-        <v/>
+      <c r="C26">
+        <v>10.62</v>
       </c>
       <c r="D26" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -776,8 +776,8 @@
       <c r="B27">
         <v>100</v>
       </c>
-      <c r="C27" t="str">
-        <v/>
+      <c r="C27">
+        <v>102.48</v>
       </c>
       <c r="D27" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -790,8 +790,8 @@
       <c r="B28">
         <v>100</v>
       </c>
-      <c r="C28" t="str">
-        <v/>
+      <c r="C28">
+        <v>76.32</v>
       </c>
       <c r="D28" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -804,8 +804,8 @@
       <c r="B29">
         <v>100</v>
       </c>
-      <c r="C29" t="str">
-        <v/>
+      <c r="C29">
+        <v>0</v>
       </c>
       <c r="D29" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -818,8 +818,8 @@
       <c r="B30">
         <v>100</v>
       </c>
-      <c r="C30" t="str">
-        <v/>
+      <c r="C30">
+        <v>39.77</v>
       </c>
       <c r="D30" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -825,9 +825,23 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="B31">
+        <v>80</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>预算设定</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -830,7 +830,7 @@
         <v>2026-10-01</v>
       </c>
       <c r="B31">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C31" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -818,8 +818,8 @@
       <c r="B30">
         <v>100</v>
       </c>
-      <c r="C30">
-        <v>39.77</v>
+      <c r="C30" t="str">
+        <v/>
       </c>
       <c r="D30" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D38"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -827,21 +827,119 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B31">
+        <v>100</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
         <v>2026-10-01</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>60</v>
       </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v>预算设定</v>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="B33">
+        <v>60</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="B34">
+        <v>60</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B35">
+        <v>60</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B36">
+        <v>60</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="B37">
+        <v>60</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B38">
+        <v>100</v>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -832,8 +832,8 @@
       <c r="B31">
         <v>100</v>
       </c>
-      <c r="C31" t="str">
-        <v/>
+      <c r="C31">
+        <v>203.21</v>
       </c>
       <c r="D31" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D43"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -846,8 +846,8 @@
       <c r="B32">
         <v>60</v>
       </c>
-      <c r="C32" t="str">
-        <v/>
+      <c r="C32">
+        <v>120</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -937,9 +937,79 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-10-08</v>
+      </c>
+      <c r="B39">
+        <v>100</v>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-10-09</v>
+      </c>
+      <c r="B40">
+        <v>100</v>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-10-10</v>
+      </c>
+      <c r="B41">
+        <v>100</v>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-10-11</v>
+      </c>
+      <c r="B42">
+        <v>100</v>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="B43">
+        <v>100</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -860,8 +860,8 @@
       <c r="B33">
         <v>60</v>
       </c>
-      <c r="C33" t="str">
-        <v/>
+      <c r="C33">
+        <v>66.42</v>
       </c>
       <c r="D33" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -874,8 +874,8 @@
       <c r="B34">
         <v>60</v>
       </c>
-      <c r="C34" t="str">
-        <v/>
+      <c r="C34">
+        <v>69.55</v>
       </c>
       <c r="D34" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -888,8 +888,8 @@
       <c r="B35">
         <v>60</v>
       </c>
-      <c r="C35" t="str">
-        <v/>
+      <c r="C35">
+        <v>103.48</v>
       </c>
       <c r="D35" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -902,8 +902,8 @@
       <c r="B36">
         <v>60</v>
       </c>
-      <c r="C36" t="str">
-        <v/>
+      <c r="C36">
+        <v>92.37</v>
       </c>
       <c r="D36" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -916,8 +916,8 @@
       <c r="B37">
         <v>60</v>
       </c>
-      <c r="C37" t="str">
-        <v/>
+      <c r="C37">
+        <v>115.1</v>
       </c>
       <c r="D37" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -930,8 +930,8 @@
       <c r="B38">
         <v>100</v>
       </c>
-      <c r="C38" t="str">
-        <v/>
+      <c r="C38">
+        <v>65.56</v>
       </c>
       <c r="D38" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -944,8 +944,8 @@
       <c r="B39">
         <v>100</v>
       </c>
-      <c r="C39" t="str">
-        <v/>
+      <c r="C39">
+        <v>55.9</v>
       </c>
       <c r="D39" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -958,8 +958,8 @@
       <c r="B40">
         <v>100</v>
       </c>
-      <c r="C40" t="str">
-        <v/>
+      <c r="C40">
+        <v>97.99</v>
       </c>
       <c r="D40" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -972,8 +972,8 @@
       <c r="B41">
         <v>100</v>
       </c>
-      <c r="C41" t="str">
-        <v/>
+      <c r="C41">
+        <v>103.99</v>
       </c>
       <c r="D41" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -986,8 +986,8 @@
       <c r="B42">
         <v>100</v>
       </c>
-      <c r="C42" t="str">
-        <v/>
+      <c r="C42">
+        <v>132.52</v>
       </c>
       <c r="D42" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -1000,16 +1000,44 @@
       <c r="B43">
         <v>100</v>
       </c>
-      <c r="C43" t="str">
-        <v/>
+      <c r="C43">
+        <v>120.13</v>
       </c>
       <c r="D43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="B44">
+        <v>100</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="B45">
+        <v>100</v>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1014,8 +1014,8 @@
       <c r="B44">
         <v>100</v>
       </c>
-      <c r="C44" t="str">
-        <v/>
+      <c r="C44">
+        <v>124.05</v>
       </c>
       <c r="D44" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D51"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -1028,16 +1028,100 @@
       <c r="B45">
         <v>100</v>
       </c>
-      <c r="C45" t="str">
-        <v/>
+      <c r="C45">
+        <v>128.87</v>
       </c>
       <c r="D45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="B47">
+        <v>100</v>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="B48">
+        <v>100</v>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-10-18</v>
+      </c>
+      <c r="B49">
+        <v>100</v>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="B50">
+        <v>100</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-10-20</v>
+      </c>
+      <c r="B51">
+        <v>100</v>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1042,8 +1042,8 @@
       <c r="B46">
         <v>100</v>
       </c>
-      <c r="C46" t="str">
-        <v/>
+      <c r="C46">
+        <v>236.46</v>
       </c>
       <c r="D46" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1056,8 +1056,8 @@
       <c r="B47">
         <v>100</v>
       </c>
-      <c r="C47" t="str">
-        <v/>
+      <c r="C47">
+        <v>119.69</v>
       </c>
       <c r="D47" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1070,8 +1070,8 @@
       <c r="B48">
         <v>100</v>
       </c>
-      <c r="C48" t="str">
-        <v/>
+      <c r="C48">
+        <v>94</v>
       </c>
       <c r="D48" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1084,8 +1084,8 @@
       <c r="B49">
         <v>100</v>
       </c>
-      <c r="C49" t="str">
-        <v/>
+      <c r="C49">
+        <v>245.46</v>
       </c>
       <c r="D49" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1098,8 +1098,8 @@
       <c r="B50">
         <v>100</v>
       </c>
-      <c r="C50" t="str">
-        <v/>
+      <c r="C50">
+        <v>119</v>
       </c>
       <c r="D50" t="str">
         <v/>

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:E58"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -418,6 +418,9 @@
       <c r="D1" t="str">
         <v>备注</v>
       </c>
+      <c r="E1" t="str">
+        <v>录入日</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -432,6 +435,9 @@
       <c r="D2" t="str">
         <v/>
       </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -446,6 +452,9 @@
       <c r="D3" t="str">
         <v/>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -460,6 +469,9 @@
       <c r="D4" t="str">
         <v/>
       </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -474,6 +486,9 @@
       <c r="D5" t="str">
         <v/>
       </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -488,6 +503,9 @@
       <c r="D6" t="str">
         <v/>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -502,6 +520,9 @@
       <c r="D7" t="str">
         <v/>
       </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -516,6 +537,9 @@
       <c r="D8" t="str">
         <v/>
       </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -530,6 +554,9 @@
       <c r="D9" t="str">
         <v/>
       </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -544,6 +571,9 @@
       <c r="D10" t="str">
         <v/>
       </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -558,6 +588,9 @@
       <c r="D11" t="str">
         <v/>
       </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -572,6 +605,9 @@
       <c r="D12" t="str">
         <v/>
       </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -586,6 +622,9 @@
       <c r="D13" t="str">
         <v/>
       </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -600,6 +639,9 @@
       <c r="D14" t="str">
         <v/>
       </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -614,6 +656,9 @@
       <c r="D15" t="str">
         <v/>
       </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -628,6 +673,9 @@
       <c r="D16" t="str">
         <v/>
       </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -642,6 +690,9 @@
       <c r="D17" t="str">
         <v/>
       </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -656,6 +707,9 @@
       <c r="D18" t="str">
         <v/>
       </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -670,6 +724,9 @@
       <c r="D19" t="str">
         <v/>
       </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -684,6 +741,9 @@
       <c r="D20" t="str">
         <v/>
       </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -698,6 +758,9 @@
       <c r="D21" t="str">
         <v/>
       </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -712,6 +775,9 @@
       <c r="D22" t="str">
         <v/>
       </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -726,6 +792,9 @@
       <c r="D23" t="str">
         <v/>
       </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -740,6 +809,9 @@
       <c r="D24" t="str">
         <v/>
       </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -754,6 +826,9 @@
       <c r="D25" t="str">
         <v/>
       </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -768,6 +843,9 @@
       <c r="D26" t="str">
         <v/>
       </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -782,6 +860,9 @@
       <c r="D27" t="str">
         <v/>
       </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -796,6 +877,9 @@
       <c r="D28" t="str">
         <v/>
       </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -810,6 +894,9 @@
       <c r="D29" t="str">
         <v/>
       </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -824,6 +911,9 @@
       <c r="D30" t="str">
         <v/>
       </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -838,6 +928,9 @@
       <c r="D31" t="str">
         <v/>
       </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -852,6 +945,9 @@
       <c r="D32" t="str">
         <v/>
       </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -866,6 +962,9 @@
       <c r="D33" t="str">
         <v/>
       </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -880,6 +979,9 @@
       <c r="D34" t="str">
         <v/>
       </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -894,6 +996,9 @@
       <c r="D35" t="str">
         <v/>
       </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -908,6 +1013,9 @@
       <c r="D36" t="str">
         <v/>
       </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -922,6 +1030,9 @@
       <c r="D37" t="str">
         <v/>
       </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -936,6 +1047,9 @@
       <c r="D38" t="str">
         <v/>
       </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -950,6 +1064,9 @@
       <c r="D39" t="str">
         <v/>
       </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -964,6 +1081,9 @@
       <c r="D40" t="str">
         <v/>
       </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -978,6 +1098,9 @@
       <c r="D41" t="str">
         <v/>
       </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -992,6 +1115,9 @@
       <c r="D42" t="str">
         <v/>
       </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1006,6 +1132,9 @@
       <c r="D43" t="str">
         <v/>
       </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1020,6 +1149,9 @@
       <c r="D44" t="str">
         <v/>
       </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1034,6 +1166,9 @@
       <c r="D45" t="str">
         <v/>
       </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1048,6 +1183,9 @@
       <c r="D46" t="str">
         <v/>
       </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1062,6 +1200,9 @@
       <c r="D47" t="str">
         <v/>
       </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1076,6 +1217,9 @@
       <c r="D48" t="str">
         <v/>
       </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1090,6 +1234,9 @@
       <c r="D49" t="str">
         <v/>
       </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -1104,6 +1251,9 @@
       <c r="D50" t="str">
         <v/>
       </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -1112,16 +1262,138 @@
       <c r="B51">
         <v>100</v>
       </c>
-      <c r="C51" t="str">
-        <v/>
+      <c r="C51">
+        <v>80.56</v>
       </c>
       <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v>2026-10-27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="B52">
+        <v>100</v>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="B53">
+        <v>100</v>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="B54">
+        <v>100</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="B55">
+        <v>100</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="B56">
+        <v>100</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="B57">
+        <v>100</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="B58">
+        <v>100</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E58"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1279,14 +1279,14 @@
       <c r="B52">
         <v>100</v>
       </c>
-      <c r="C52" t="str">
-        <v/>
+      <c r="C52">
+        <v>62.56</v>
       </c>
       <c r="D52" t="str">
         <v/>
       </c>
       <c r="E52" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
     </row>
     <row r="53">

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1296,14 +1296,14 @@
       <c r="B53">
         <v>100</v>
       </c>
-      <c r="C53" t="str">
-        <v/>
+      <c r="C53">
+        <v>57.66</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
     </row>
     <row r="54">

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1313,14 +1313,14 @@
       <c r="B54">
         <v>100</v>
       </c>
-      <c r="C54" t="str">
-        <v/>
+      <c r="C54">
+        <v>6.5</v>
       </c>
       <c r="D54" t="str">
         <v/>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
     </row>
     <row r="55">

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1330,14 +1330,14 @@
       <c r="B55">
         <v>100</v>
       </c>
-      <c r="C55" t="str">
-        <v/>
+      <c r="C55">
+        <v>66.62</v>
       </c>
       <c r="D55" t="str">
         <v/>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
     </row>
     <row r="56">

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1347,14 +1347,14 @@
       <c r="B56">
         <v>100</v>
       </c>
-      <c r="C56" t="str">
-        <v/>
+      <c r="C56">
+        <v>218.72</v>
       </c>
       <c r="D56" t="str">
         <v/>
       </c>
       <c r="E56" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
     </row>
     <row r="57">

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1364,14 +1364,14 @@
       <c r="B57">
         <v>100</v>
       </c>
-      <c r="C57" t="str">
-        <v/>
+      <c r="C57">
+        <v>200</v>
       </c>
       <c r="D57" t="str">
         <v/>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>2026-10-27</v>
       </c>
     </row>
     <row r="58">

--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E60"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -1381,19 +1381,53 @@
       <c r="B58">
         <v>100</v>
       </c>
-      <c r="C58" t="str">
-        <v/>
+      <c r="C58">
+        <v>79</v>
       </c>
       <c r="D58" t="str">
         <v/>
       </c>
       <c r="E58" t="str">
+        <v>2026-10-29</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="B59">
+        <v>100</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="B60">
+        <v>100</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E60"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/budget.xlsx
+++ b/data/budget.xlsx
@@ -1398,14 +1398,14 @@
       <c r="B59">
         <v>100</v>
       </c>
-      <c r="C59" t="str">
-        <v/>
+      <c r="C59">
+        <v>70</v>
       </c>
       <c r="D59" t="str">
         <v/>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>2026-10-29</v>
       </c>
     </row>
     <row r="60">
